--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -503,6 +504,11 @@
           <t>Locked until</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Must change password</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -540,77 +546,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>pbkdf2_sha256$260000$f2c629354d844744b015737641e6f92d$ae21b37e00a0d6e7132c6d513f9440c6eb2f31fe7ad80e0d92496d2ae472c7b4</t>
+          <t>pbkdf2_sha256$260000$a6233b3818393e8a62eb7a9f2c13da4f$7babef5dca7c25572cc9d48f49419a08886396cb937a1f2cf9c644e83d150e44</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-24T20:46:48</t>
+          <t>2026-09-26T12:16:40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-24T21:10:58</t>
+          <t>2026-09-26T12:17:54</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Esam</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Mohamed</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>isammohamed781@gmail.com</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2002-01-18</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>pbkdf2_sha256$260000$30ff73671cc5cf0d47fc7b1607879eb7$95e6e4e266887191c3f0073490dfb1d2505b30ca10234ed02e05e119c7fad8f0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-09-24T21:16:40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-09-24T21:16:40</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -425,22 +425,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,60 +456,85 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Patient ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>First name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Birth date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marital status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Diabetes type</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Dial code</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Password hash</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Created at</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Last login</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Failed attempts</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Locked until</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Must change password</t>
         </is>
@@ -516,54 +546,161 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>26092901</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Esam</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Mohamed</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>isammohd781@gmail.com</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>2002-01-18</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>pbkdf2_sha256$260000$a6233b3818393e8a62eb7a9f2c13da4f$7babef5dca7c25572cc9d48f49419a08886396cb937a1f2cf9c644e83d150e44</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:16:40</t>
+          <t>type1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:17:54</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>+256</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>+256771715275</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>pbkdf2_sha256$260000$a957f6add75ac6b0447149c0d18ca856$b9874468dd08f5b6ae821f4a699652a62cb3e62a210cc213c87f837680f6bb09</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:16:19</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:17:43</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>26092901</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>isammohamed781@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>not_sure</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>+256</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>+256771715275</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>pbkdf2_sha256$260000$105b3b52cfbc787d1f056db5af85f6c2$8b58f5f73e074e7afb663222efc58ed2f07cdc4aafab70e77d9183420e2c917d</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:05:46</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:05:46</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-09-29T23:17:43</t>
+          <t>2026-09-30T15:50:36</t>
         </is>
       </c>
       <c r="P2" t="n">

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -539,6 +539,11 @@
           <t>Must change password</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Profile photo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -546,7 +551,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26092901</t>
+          <t>26100101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -581,7 +586,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>type1</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,17 +606,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>pbkdf2_sha256$260000$a957f6add75ac6b0447149c0d18ca856$b9874468dd08f5b6ae821f4a699652a62cb3e62a210cc213c87f837680f6bb09</t>
+          <t>pbkdf2_sha256$260000$fc0ec15b3098752609bf2bb5a603bfbc$67150f59dac7fce505b85bc31c4d64ff2c2b0bf8635df5d2fef7e124d597ca08</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-29T22:16:19</t>
+          <t>2026-10-01T03:48:42</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-09-30T15:50:36</t>
+          <t>2026-10-01T04:09:28</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -621,88 +626,7 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>26092901</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Esam</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mohamed</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>isammohamed781@gmail.com</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>not_sure</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>+256</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>+256771715275</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>pbkdf2_sha256$260000$105b3b52cfbc787d1f056db5af85f6c2$8b58f5f73e074e7afb663222efc58ed2f07cdc4aafab70e77d9183420e2c917d</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-09-29T23:05:46</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2026-09-29T23:05:46</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -606,17 +606,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>pbkdf2_sha256$260000$fc0ec15b3098752609bf2bb5a603bfbc$67150f59dac7fce505b85bc31c4d64ff2c2b0bf8635df5d2fef7e124d597ca08</t>
+          <t>pbkdf2_sha256$260000$6b9b4e32d92613c28ad035fa7b949cc7$5d44dd42020efd4be7c09243b9083788d88f522c739d1b07527502027c0caad2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-01T03:48:42</t>
+          <t>2026-10-01T17:55:17</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-01T04:09:28</t>
+          <t>2026-10-01T17:55:17</t>
         </is>
       </c>
       <c r="P2" t="n">
